--- a/resources/analysis_schema_quant_data_analysis_nutrition_template.xlsx
+++ b/resources/analysis_schema_quant_data_analysis_nutrition_template.xlsx
@@ -1,34 +1,142 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573FCA66-6E73-47C9-A357-8924DCAAEA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-28905" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Indicators" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Indicators" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
+  <si>
+    <t>indicator_name</t>
+  </si>
+  <si>
+    <t>calculation</t>
+  </si>
+  <si>
+    <t>var_name</t>
+  </si>
+  <si>
+    <t>denom_var</t>
+  </si>
+  <si>
+    <t>disaggregation</t>
+  </si>
+  <si>
+    <t>multiplier</t>
+  </si>
+  <si>
+    <t>indicator_unit</t>
+  </si>
+  <si>
+    <t>prop</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>MUAC (cm) - Mean</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>nut_muac_cm</t>
+  </si>
+  <si>
+    <t>cm</t>
+  </si>
+  <si>
+    <t>gam_muac</t>
+  </si>
+  <si>
+    <t>cat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severe Acute Malnutrition by MUAC (SAM) </t>
+  </si>
+  <si>
+    <t>Moderate Acute Malnutrition by MUAC (MAM)</t>
+  </si>
+  <si>
+    <t>Global Acute Malnutrition by MUAC (GAM)</t>
+  </si>
+  <si>
+    <t>mam_muac</t>
+  </si>
+  <si>
+    <t>sam_muac</t>
+  </si>
+  <si>
+    <t>Global Acute Malnutrition by MFAZ (GAM)</t>
+  </si>
+  <si>
+    <t>Moderate Acute Malnutrition by MFAZ (MAM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severe Acute Malnutrition by MFAZ (SAM) </t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-Score (MFAZ)</t>
+  </si>
+  <si>
+    <t>mfaz</t>
+  </si>
+  <si>
+    <t>global_mfaz</t>
+  </si>
+  <si>
+    <t>moderate_mfaz</t>
+  </si>
+  <si>
+    <t>severe_mfaz</t>
+  </si>
+  <si>
+    <t>Early Childhood Food Insecurity Score (ECFIES) - Mean</t>
+  </si>
+  <si>
+    <t>nut_ecfies_score</t>
+  </si>
+  <si>
+    <t>score</t>
+  </si>
+  <si>
+    <t>Early Childhood Food Insecurity Score (ECFIES) - Category</t>
+  </si>
+  <si>
+    <t>nut_ecfies_cat</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +155,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,142 +457,207 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>indicator_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>calculation</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>var_name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>denom_var</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>disaggregation</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>multiplier</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>indicator_unit</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Global Acute Malnutrition (GAM)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>gam_yn</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>admin1</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3">
         <v>100</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Severe Acute Malnutrition (SAM)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>sam_yn</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>admin1</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4">
         <v>100</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Stunting prevalence</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>prop</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>stunting_yn</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>admin1</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+      <c r="G4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5">
         <v>100</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+      <c r="G5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>100</v>
+      </c>
+      <c r="G7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11">
+        <v>100</v>
+      </c>
+      <c r="G11" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/resources/analysis_schema_quant_data_analysis_nutrition_template.xlsx
+++ b/resources/analysis_schema_quant_data_analysis_nutrition_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573FCA66-6E73-47C9-A357-8924DCAAEA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6807641D-23F0-4545-839B-6F86C8E8D8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28905" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicators" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
   <si>
     <t>indicator_name</t>
   </si>
@@ -67,21 +67,9 @@
     <t>cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Severe Acute Malnutrition by MUAC (SAM) </t>
-  </si>
-  <si>
-    <t>Moderate Acute Malnutrition by MUAC (MAM)</t>
-  </si>
-  <si>
     <t>Global Acute Malnutrition by MUAC (GAM)</t>
   </si>
   <si>
-    <t>mam_muac</t>
-  </si>
-  <si>
-    <t>sam_muac</t>
-  </si>
-  <si>
     <t>Global Acute Malnutrition by MFAZ (GAM)</t>
   </si>
   <si>
@@ -119,6 +107,12 @@
   </si>
   <si>
     <t>nut_ecfies_cat</t>
+  </si>
+  <si>
+    <t>Nutritional Status by MUAC</t>
+  </si>
+  <si>
+    <t>nut_muac_cat</t>
   </si>
 </sst>
 </file>
@@ -458,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.85546875" customWidth="1"/>
@@ -512,7 +506,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -529,13 +523,13 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -546,44 +540,44 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="G6" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -594,13 +588,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -611,52 +605,35 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
       <c r="F10">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11">
-        <v>100</v>
-      </c>
-      <c r="G11" t="s">
         <v>8</v>
       </c>
     </row>

--- a/resources/analysis_schema_quant_data_analysis_nutrition_template.xlsx
+++ b/resources/analysis_schema_quant_data_analysis_nutrition_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6807641D-23F0-4545-839B-6F86C8E8D8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CE1D95-ED12-4115-A1B7-1DCA43E148BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicators" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="80">
   <si>
     <t>indicator_name</t>
   </si>
@@ -82,9 +82,6 @@
     <t>MUAC-for-Age Z-Score (MFAZ)</t>
   </si>
   <si>
-    <t>mfaz</t>
-  </si>
-  <si>
     <t>global_mfaz</t>
   </si>
   <si>
@@ -113,16 +110,172 @@
   </si>
   <si>
     <t>nut_muac_cat</t>
+  </si>
+  <si>
+    <t>nut_mfaz</t>
+  </si>
+  <si>
+    <t>nut_mfaz_noflag</t>
+  </si>
+  <si>
+    <t>nut_muac_cat_noflag</t>
+  </si>
+  <si>
+    <t>Nutritional Edema</t>
+  </si>
+  <si>
+    <t>nut_edema_confirm</t>
+  </si>
+  <si>
+    <t>nut_muac_cm_noflag</t>
+  </si>
+  <si>
+    <t>gam_muac_noflag</t>
+  </si>
+  <si>
+    <t>global_mfaz_noflag</t>
+  </si>
+  <si>
+    <t>moderate_mfaz_noflag</t>
+  </si>
+  <si>
+    <t>severe_mfaz_noflag</t>
+  </si>
+  <si>
+    <t>MUAC (cm) - Mean (flags excluded)</t>
+  </si>
+  <si>
+    <t>Global Acute Malnutrition by MUAC (GAM) (flags excluded)</t>
+  </si>
+  <si>
+    <t>Nutritional Status by MUAC (flags excluded)</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-Score (MFAZ) (flags excluded)</t>
+  </si>
+  <si>
+    <t>Global Acute Malnutrition by MFAZ (GAM) (flags excluded)</t>
+  </si>
+  <si>
+    <t>Moderate Acute Malnutrition by MFAZ (MAM) (flags excluded)</t>
+  </si>
+  <si>
+    <t>Severe Acute Malnutrition by MFAZ (SAM)  (flags excluded)</t>
+  </si>
+  <si>
+    <t>ECFIES - Worried Child Eats Enough</t>
+  </si>
+  <si>
+    <t>ECFIES - Unable Nutritious Foods</t>
+  </si>
+  <si>
+    <t>ECFIES - Fewer Foods</t>
+  </si>
+  <si>
+    <t>ECFIES - Skipped Meals</t>
+  </si>
+  <si>
+    <t>ECFIES - Less Food Amount</t>
+  </si>
+  <si>
+    <t>ECFIES - Household Out of Food</t>
+  </si>
+  <si>
+    <t>ECFIES - Child Hungry</t>
+  </si>
+  <si>
+    <t>ECFIES - Whole Day No Food</t>
+  </si>
+  <si>
+    <t>CMAM Enrollment</t>
+  </si>
+  <si>
+    <t>nut_cmam_enrollment</t>
+  </si>
+  <si>
+    <t>Caregiver Present</t>
+  </si>
+  <si>
+    <t>nut_caregiver_present</t>
+  </si>
+  <si>
+    <t>Child Present</t>
+  </si>
+  <si>
+    <t>nut_child_present</t>
+  </si>
+  <si>
+    <t>Breastfed Yesterday</t>
+  </si>
+  <si>
+    <t>nut_bf_yesterday</t>
+  </si>
+  <si>
+    <t>Reasons Not Breastfed</t>
+  </si>
+  <si>
+    <t>nut_bf_lack_reasons</t>
+  </si>
+  <si>
+    <t>Food Consumed Yesterday</t>
+  </si>
+  <si>
+    <t>nut_food_child_consumptions</t>
+  </si>
+  <si>
+    <t>Complementary Feeding Challenges</t>
+  </si>
+  <si>
+    <t>nut_complementary_feeding_challenges</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>stratum</t>
+  </si>
+  <si>
+    <t>age_months_cat</t>
+  </si>
+  <si>
+    <t>ecfies_s01</t>
+  </si>
+  <si>
+    <t>ecfies_s02</t>
+  </si>
+  <si>
+    <t>ecfies_s03</t>
+  </si>
+  <si>
+    <t>ecfies_s04</t>
+  </si>
+  <si>
+    <t>ecfies_s05</t>
+  </si>
+  <si>
+    <t>ecfies_s06</t>
+  </si>
+  <si>
+    <t>ecfies_s07</t>
+  </si>
+  <si>
+    <t>ecfies_s08</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -452,14 +605,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.85546875" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -489,30 +642,30 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="F3">
         <v>100</v>
@@ -523,44 +676,47 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="G5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -571,30 +727,27 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -605,39 +758,2330 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10">
+        <v>100</v>
+      </c>
+      <c r="G10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12">
+        <v>100</v>
+      </c>
+      <c r="G12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13">
+        <v>100</v>
+      </c>
+      <c r="G13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15">
+        <v>100</v>
+      </c>
+      <c r="G15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16">
+        <v>100</v>
+      </c>
+      <c r="G16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17">
+        <v>100</v>
+      </c>
+      <c r="G17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18">
+        <v>100</v>
+      </c>
+      <c r="G18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
         <v>27</v>
       </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="F20">
+        <v>100</v>
+      </c>
+      <c r="G20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21">
+        <v>100</v>
+      </c>
+      <c r="G21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22">
+        <v>100</v>
+      </c>
+      <c r="G22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23">
+        <v>100</v>
+      </c>
+      <c r="G23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24">
+        <v>100</v>
+      </c>
+      <c r="G24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25">
+        <v>100</v>
+      </c>
+      <c r="G25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26">
+        <v>100</v>
+      </c>
+      <c r="G26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27">
+        <v>100</v>
+      </c>
+      <c r="G27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28">
+        <v>100</v>
+      </c>
+      <c r="G28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>56</v>
+      </c>
+      <c r="F29">
+        <v>100</v>
+      </c>
+      <c r="G29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>62</v>
+      </c>
+      <c r="F30">
+        <v>100</v>
+      </c>
+      <c r="G30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
+        <v>64</v>
+      </c>
+      <c r="F31">
+        <v>100</v>
+      </c>
+      <c r="G31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
+      </c>
+      <c r="F32">
+        <v>100</v>
+      </c>
+      <c r="G32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>67</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="F33">
+        <v>100</v>
+      </c>
+      <c r="G33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F34">
+        <v>100</v>
+      </c>
+      <c r="G34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>60</v>
+      </c>
+      <c r="E35" t="s">
+        <v>69</v>
+      </c>
+      <c r="F35">
+        <v>100</v>
+      </c>
+      <c r="G35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>69</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s">
+        <v>69</v>
+      </c>
+      <c r="F37">
+        <v>100</v>
+      </c>
+      <c r="G37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>28</v>
       </c>
-      <c r="F10">
-        <v>100</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="B38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" t="s">
+        <v>69</v>
+      </c>
+      <c r="F38">
+        <v>100</v>
+      </c>
+      <c r="G38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" t="s">
+        <v>69</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" t="s">
+        <v>69</v>
+      </c>
+      <c r="F40">
+        <v>100</v>
+      </c>
+      <c r="G40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" t="s">
+        <v>69</v>
+      </c>
+      <c r="F41">
+        <v>100</v>
+      </c>
+      <c r="G41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" t="s">
+        <v>69</v>
+      </c>
+      <c r="F42">
+        <v>100</v>
+      </c>
+      <c r="G42" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" t="s">
+        <v>35</v>
+      </c>
+      <c r="E43" t="s">
+        <v>69</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E44" t="s">
+        <v>69</v>
+      </c>
+      <c r="F44">
+        <v>100</v>
+      </c>
+      <c r="G44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" t="s">
+        <v>32</v>
+      </c>
+      <c r="E45" t="s">
+        <v>69</v>
+      </c>
+      <c r="F45">
+        <v>100</v>
+      </c>
+      <c r="G45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" t="s">
+        <v>31</v>
+      </c>
+      <c r="E46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" t="s">
+        <v>37</v>
+      </c>
+      <c r="E47" t="s">
+        <v>69</v>
+      </c>
+      <c r="F47">
+        <v>100</v>
+      </c>
+      <c r="G47" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" t="s">
+        <v>38</v>
+      </c>
+      <c r="E48" t="s">
+        <v>69</v>
+      </c>
+      <c r="F48">
+        <v>100</v>
+      </c>
+      <c r="G48" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>46</v>
+      </c>
+      <c r="B49" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" t="s">
+        <v>39</v>
+      </c>
+      <c r="E49" t="s">
+        <v>69</v>
+      </c>
+      <c r="F49">
+        <v>100</v>
+      </c>
+      <c r="G49" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>33</v>
+      </c>
+      <c r="B50" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" t="s">
+        <v>34</v>
+      </c>
+      <c r="E50" t="s">
+        <v>69</v>
+      </c>
+      <c r="F50">
+        <v>100</v>
+      </c>
+      <c r="G50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" t="s">
+        <v>69</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" t="s">
+        <v>27</v>
+      </c>
+      <c r="E52" t="s">
+        <v>69</v>
+      </c>
+      <c r="F52">
+        <v>100</v>
+      </c>
+      <c r="G52" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>47</v>
+      </c>
+      <c r="B53" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" t="s">
+        <v>72</v>
+      </c>
+      <c r="E53" t="s">
+        <v>69</v>
+      </c>
+      <c r="F53">
+        <v>100</v>
+      </c>
+      <c r="G53" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>48</v>
+      </c>
+      <c r="B54" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" t="s">
+        <v>69</v>
+      </c>
+      <c r="F54">
+        <v>100</v>
+      </c>
+      <c r="G54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>49</v>
+      </c>
+      <c r="B55" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55" t="s">
+        <v>74</v>
+      </c>
+      <c r="E55" t="s">
+        <v>69</v>
+      </c>
+      <c r="F55">
+        <v>100</v>
+      </c>
+      <c r="G55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>50</v>
+      </c>
+      <c r="B56" t="s">
+        <v>14</v>
+      </c>
+      <c r="C56" t="s">
+        <v>75</v>
+      </c>
+      <c r="E56" t="s">
+        <v>69</v>
+      </c>
+      <c r="F56">
+        <v>100</v>
+      </c>
+      <c r="G56" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>51</v>
+      </c>
+      <c r="B57" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57" t="s">
+        <v>76</v>
+      </c>
+      <c r="E57" t="s">
+        <v>69</v>
+      </c>
+      <c r="F57">
+        <v>100</v>
+      </c>
+      <c r="G57" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>52</v>
+      </c>
+      <c r="B58" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" t="s">
+        <v>77</v>
+      </c>
+      <c r="E58" t="s">
+        <v>69</v>
+      </c>
+      <c r="F58">
+        <v>100</v>
+      </c>
+      <c r="G58" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>53</v>
+      </c>
+      <c r="B59" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59" t="s">
+        <v>78</v>
+      </c>
+      <c r="E59" t="s">
+        <v>69</v>
+      </c>
+      <c r="F59">
+        <v>100</v>
+      </c>
+      <c r="G59" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>54</v>
+      </c>
+      <c r="B60" t="s">
+        <v>14</v>
+      </c>
+      <c r="C60" t="s">
+        <v>79</v>
+      </c>
+      <c r="E60" t="s">
+        <v>69</v>
+      </c>
+      <c r="F60">
+        <v>100</v>
+      </c>
+      <c r="G60" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>55</v>
+      </c>
+      <c r="B61" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" t="s">
+        <v>56</v>
+      </c>
+      <c r="E61" t="s">
+        <v>69</v>
+      </c>
+      <c r="F61">
+        <v>100</v>
+      </c>
+      <c r="G61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62" t="s">
+        <v>62</v>
+      </c>
+      <c r="E62" t="s">
+        <v>69</v>
+      </c>
+      <c r="F62">
+        <v>100</v>
+      </c>
+      <c r="G62" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+      <c r="B63" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" t="s">
+        <v>64</v>
+      </c>
+      <c r="E63" t="s">
+        <v>69</v>
+      </c>
+      <c r="F63">
+        <v>100</v>
+      </c>
+      <c r="G63" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>65</v>
+      </c>
+      <c r="B64" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" t="s">
+        <v>66</v>
+      </c>
+      <c r="E64" t="s">
+        <v>69</v>
+      </c>
+      <c r="F64">
+        <v>100</v>
+      </c>
+      <c r="G64" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>67</v>
+      </c>
+      <c r="B65" t="s">
+        <v>14</v>
+      </c>
+      <c r="C65" t="s">
+        <v>68</v>
+      </c>
+      <c r="E65" t="s">
+        <v>69</v>
+      </c>
+      <c r="F65">
+        <v>100</v>
+      </c>
+      <c r="G65" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>57</v>
+      </c>
+      <c r="B66" t="s">
+        <v>14</v>
+      </c>
+      <c r="C66" t="s">
+        <v>58</v>
+      </c>
+      <c r="E66" t="s">
+        <v>70</v>
+      </c>
+      <c r="F66">
+        <v>100</v>
+      </c>
+      <c r="G66" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>59</v>
+      </c>
+      <c r="B67" t="s">
+        <v>14</v>
+      </c>
+      <c r="C67" t="s">
+        <v>60</v>
+      </c>
+      <c r="E67" t="s">
+        <v>70</v>
+      </c>
+      <c r="F67">
+        <v>100</v>
+      </c>
+      <c r="G67" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>9</v>
+      </c>
+      <c r="B68" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" t="s">
+        <v>70</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" t="s">
+        <v>70</v>
+      </c>
+      <c r="F69">
+        <v>100</v>
+      </c>
+      <c r="G69" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>28</v>
+      </c>
+      <c r="B70" t="s">
+        <v>14</v>
+      </c>
+      <c r="C70" t="s">
+        <v>29</v>
+      </c>
+      <c r="E70" t="s">
+        <v>70</v>
+      </c>
+      <c r="F70">
+        <v>100</v>
+      </c>
+      <c r="G70" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>19</v>
+      </c>
+      <c r="B71" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s">
+        <v>30</v>
+      </c>
+      <c r="E71" t="s">
+        <v>70</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>16</v>
+      </c>
+      <c r="B72" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" t="s">
+        <v>70</v>
+      </c>
+      <c r="F72">
+        <v>100</v>
+      </c>
+      <c r="G72" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>17</v>
+      </c>
+      <c r="B73" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" t="s">
+        <v>21</v>
+      </c>
+      <c r="E73" t="s">
+        <v>70</v>
+      </c>
+      <c r="F73">
+        <v>100</v>
+      </c>
+      <c r="G73" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>18</v>
+      </c>
+      <c r="B74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" t="s">
+        <v>22</v>
+      </c>
+      <c r="E74" t="s">
+        <v>70</v>
+      </c>
+      <c r="F74">
+        <v>100</v>
+      </c>
+      <c r="G74" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>40</v>
+      </c>
+      <c r="B75" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" t="s">
+        <v>35</v>
+      </c>
+      <c r="E75" t="s">
+        <v>70</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>41</v>
+      </c>
+      <c r="B76" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" t="s">
+        <v>36</v>
+      </c>
+      <c r="E76" t="s">
+        <v>70</v>
+      </c>
+      <c r="F76">
+        <v>100</v>
+      </c>
+      <c r="G76" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>42</v>
+      </c>
+      <c r="B77" t="s">
+        <v>14</v>
+      </c>
+      <c r="C77" t="s">
+        <v>32</v>
+      </c>
+      <c r="E77" t="s">
+        <v>70</v>
+      </c>
+      <c r="F77">
+        <v>100</v>
+      </c>
+      <c r="G77" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>43</v>
+      </c>
+      <c r="B78" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" t="s">
+        <v>31</v>
+      </c>
+      <c r="E78" t="s">
+        <v>70</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>44</v>
+      </c>
+      <c r="B79" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" t="s">
+        <v>37</v>
+      </c>
+      <c r="E79" t="s">
+        <v>70</v>
+      </c>
+      <c r="F79">
+        <v>100</v>
+      </c>
+      <c r="G79" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>45</v>
+      </c>
+      <c r="B80" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" t="s">
+        <v>38</v>
+      </c>
+      <c r="E80" t="s">
+        <v>70</v>
+      </c>
+      <c r="F80">
+        <v>100</v>
+      </c>
+      <c r="G80" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>46</v>
+      </c>
+      <c r="B81" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" t="s">
+        <v>39</v>
+      </c>
+      <c r="E81" t="s">
+        <v>70</v>
+      </c>
+      <c r="F81">
+        <v>100</v>
+      </c>
+      <c r="G81" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>33</v>
+      </c>
+      <c r="B82" t="s">
+        <v>14</v>
+      </c>
+      <c r="C82" t="s">
+        <v>34</v>
+      </c>
+      <c r="E82" t="s">
+        <v>70</v>
+      </c>
+      <c r="F82">
+        <v>100</v>
+      </c>
+      <c r="G82" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>23</v>
+      </c>
+      <c r="B83" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" t="s">
+        <v>24</v>
+      </c>
+      <c r="E83" t="s">
+        <v>70</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="G83" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>26</v>
+      </c>
+      <c r="B84" t="s">
+        <v>14</v>
+      </c>
+      <c r="C84" t="s">
+        <v>27</v>
+      </c>
+      <c r="E84" t="s">
+        <v>70</v>
+      </c>
+      <c r="F84">
+        <v>100</v>
+      </c>
+      <c r="G84" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>47</v>
+      </c>
+      <c r="B85" t="s">
+        <v>14</v>
+      </c>
+      <c r="C85" t="s">
+        <v>72</v>
+      </c>
+      <c r="E85" t="s">
+        <v>70</v>
+      </c>
+      <c r="F85">
+        <v>100</v>
+      </c>
+      <c r="G85" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>48</v>
+      </c>
+      <c r="B86" t="s">
+        <v>14</v>
+      </c>
+      <c r="C86" t="s">
+        <v>73</v>
+      </c>
+      <c r="E86" t="s">
+        <v>70</v>
+      </c>
+      <c r="F86">
+        <v>100</v>
+      </c>
+      <c r="G86" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>49</v>
+      </c>
+      <c r="B87" t="s">
+        <v>14</v>
+      </c>
+      <c r="C87" t="s">
+        <v>74</v>
+      </c>
+      <c r="E87" t="s">
+        <v>70</v>
+      </c>
+      <c r="F87">
+        <v>100</v>
+      </c>
+      <c r="G87" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>50</v>
+      </c>
+      <c r="B88" t="s">
+        <v>14</v>
+      </c>
+      <c r="C88" t="s">
+        <v>75</v>
+      </c>
+      <c r="E88" t="s">
+        <v>70</v>
+      </c>
+      <c r="F88">
+        <v>100</v>
+      </c>
+      <c r="G88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>51</v>
+      </c>
+      <c r="B89" t="s">
+        <v>14</v>
+      </c>
+      <c r="C89" t="s">
+        <v>76</v>
+      </c>
+      <c r="E89" t="s">
+        <v>70</v>
+      </c>
+      <c r="F89">
+        <v>100</v>
+      </c>
+      <c r="G89" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>52</v>
+      </c>
+      <c r="B90" t="s">
+        <v>14</v>
+      </c>
+      <c r="C90" t="s">
+        <v>77</v>
+      </c>
+      <c r="E90" t="s">
+        <v>70</v>
+      </c>
+      <c r="F90">
+        <v>100</v>
+      </c>
+      <c r="G90" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>53</v>
+      </c>
+      <c r="B91" t="s">
+        <v>14</v>
+      </c>
+      <c r="C91" t="s">
+        <v>78</v>
+      </c>
+      <c r="E91" t="s">
+        <v>70</v>
+      </c>
+      <c r="F91">
+        <v>100</v>
+      </c>
+      <c r="G91" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>54</v>
+      </c>
+      <c r="B92" t="s">
+        <v>14</v>
+      </c>
+      <c r="C92" t="s">
+        <v>79</v>
+      </c>
+      <c r="E92" t="s">
+        <v>70</v>
+      </c>
+      <c r="F92">
+        <v>100</v>
+      </c>
+      <c r="G92" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>55</v>
+      </c>
+      <c r="B93" t="s">
+        <v>14</v>
+      </c>
+      <c r="C93" t="s">
+        <v>56</v>
+      </c>
+      <c r="E93" t="s">
+        <v>70</v>
+      </c>
+      <c r="F93">
+        <v>100</v>
+      </c>
+      <c r="G93" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>61</v>
+      </c>
+      <c r="B94" t="s">
+        <v>14</v>
+      </c>
+      <c r="C94" t="s">
+        <v>62</v>
+      </c>
+      <c r="E94" t="s">
+        <v>70</v>
+      </c>
+      <c r="F94">
+        <v>100</v>
+      </c>
+      <c r="G94" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>63</v>
+      </c>
+      <c r="B95" t="s">
+        <v>14</v>
+      </c>
+      <c r="C95" t="s">
+        <v>64</v>
+      </c>
+      <c r="E95" t="s">
+        <v>70</v>
+      </c>
+      <c r="F95">
+        <v>100</v>
+      </c>
+      <c r="G95" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>65</v>
+      </c>
+      <c r="B96" t="s">
+        <v>14</v>
+      </c>
+      <c r="C96" t="s">
+        <v>66</v>
+      </c>
+      <c r="E96" t="s">
+        <v>70</v>
+      </c>
+      <c r="F96">
+        <v>100</v>
+      </c>
+      <c r="G96" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>67</v>
+      </c>
+      <c r="B97" t="s">
+        <v>14</v>
+      </c>
+      <c r="C97" t="s">
+        <v>68</v>
+      </c>
+      <c r="E97" t="s">
+        <v>70</v>
+      </c>
+      <c r="F97">
+        <v>100</v>
+      </c>
+      <c r="G97" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>57</v>
+      </c>
+      <c r="B98" t="s">
+        <v>14</v>
+      </c>
+      <c r="C98" t="s">
+        <v>58</v>
+      </c>
+      <c r="E98" t="s">
+        <v>71</v>
+      </c>
+      <c r="F98">
+        <v>100</v>
+      </c>
+      <c r="G98" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>59</v>
+      </c>
+      <c r="B99" t="s">
+        <v>14</v>
+      </c>
+      <c r="C99" t="s">
+        <v>60</v>
+      </c>
+      <c r="E99" t="s">
+        <v>71</v>
+      </c>
+      <c r="F99">
+        <v>100</v>
+      </c>
+      <c r="G99" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>9</v>
+      </c>
+      <c r="B100" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" t="s">
+        <v>71</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" t="s">
+        <v>71</v>
+      </c>
+      <c r="F101">
+        <v>100</v>
+      </c>
+      <c r="G101" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>28</v>
+      </c>
+      <c r="B102" t="s">
+        <v>14</v>
+      </c>
+      <c r="C102" t="s">
+        <v>29</v>
+      </c>
+      <c r="E102" t="s">
+        <v>71</v>
+      </c>
+      <c r="F102">
+        <v>100</v>
+      </c>
+      <c r="G102" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>19</v>
+      </c>
+      <c r="B103" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" t="s">
+        <v>30</v>
+      </c>
+      <c r="E103" t="s">
+        <v>71</v>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>16</v>
+      </c>
+      <c r="B104" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" t="s">
+        <v>20</v>
+      </c>
+      <c r="E104" t="s">
+        <v>71</v>
+      </c>
+      <c r="F104">
+        <v>100</v>
+      </c>
+      <c r="G104" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>17</v>
+      </c>
+      <c r="B105" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" t="s">
+        <v>21</v>
+      </c>
+      <c r="E105" t="s">
+        <v>71</v>
+      </c>
+      <c r="F105">
+        <v>100</v>
+      </c>
+      <c r="G105" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>18</v>
+      </c>
+      <c r="B106" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" t="s">
+        <v>22</v>
+      </c>
+      <c r="E106" t="s">
+        <v>71</v>
+      </c>
+      <c r="F106">
+        <v>100</v>
+      </c>
+      <c r="G106" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>40</v>
+      </c>
+      <c r="B107" t="s">
+        <v>10</v>
+      </c>
+      <c r="C107" t="s">
+        <v>35</v>
+      </c>
+      <c r="E107" t="s">
+        <v>71</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+      <c r="G107" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>41</v>
+      </c>
+      <c r="B108" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108" t="s">
+        <v>36</v>
+      </c>
+      <c r="E108" t="s">
+        <v>71</v>
+      </c>
+      <c r="F108">
+        <v>100</v>
+      </c>
+      <c r="G108" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>42</v>
+      </c>
+      <c r="B109" t="s">
+        <v>14</v>
+      </c>
+      <c r="C109" t="s">
+        <v>32</v>
+      </c>
+      <c r="E109" t="s">
+        <v>71</v>
+      </c>
+      <c r="F109">
+        <v>100</v>
+      </c>
+      <c r="G109" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>43</v>
+      </c>
+      <c r="B110" t="s">
+        <v>10</v>
+      </c>
+      <c r="C110" t="s">
+        <v>31</v>
+      </c>
+      <c r="E110" t="s">
+        <v>71</v>
+      </c>
+      <c r="F110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>44</v>
+      </c>
+      <c r="B111" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" t="s">
+        <v>37</v>
+      </c>
+      <c r="E111" t="s">
+        <v>71</v>
+      </c>
+      <c r="F111">
+        <v>100</v>
+      </c>
+      <c r="G111" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>45</v>
+      </c>
+      <c r="B112" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" t="s">
+        <v>38</v>
+      </c>
+      <c r="E112" t="s">
+        <v>71</v>
+      </c>
+      <c r="F112">
+        <v>100</v>
+      </c>
+      <c r="G112" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>46</v>
+      </c>
+      <c r="B113" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" t="s">
+        <v>39</v>
+      </c>
+      <c r="E113" t="s">
+        <v>71</v>
+      </c>
+      <c r="F113">
+        <v>100</v>
+      </c>
+      <c r="G113" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>33</v>
+      </c>
+      <c r="B114" t="s">
+        <v>14</v>
+      </c>
+      <c r="C114" t="s">
+        <v>34</v>
+      </c>
+      <c r="E114" t="s">
+        <v>71</v>
+      </c>
+      <c r="F114">
+        <v>100</v>
+      </c>
+      <c r="G114" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>23</v>
+      </c>
+      <c r="B115" t="s">
+        <v>10</v>
+      </c>
+      <c r="C115" t="s">
+        <v>24</v>
+      </c>
+      <c r="E115" t="s">
+        <v>71</v>
+      </c>
+      <c r="F115">
+        <v>1</v>
+      </c>
+      <c r="G115" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>26</v>
+      </c>
+      <c r="B116" t="s">
+        <v>14</v>
+      </c>
+      <c r="C116" t="s">
+        <v>27</v>
+      </c>
+      <c r="E116" t="s">
+        <v>71</v>
+      </c>
+      <c r="F116">
+        <v>100</v>
+      </c>
+      <c r="G116" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>47</v>
+      </c>
+      <c r="B117" t="s">
+        <v>14</v>
+      </c>
+      <c r="C117" t="s">
+        <v>72</v>
+      </c>
+      <c r="E117" t="s">
+        <v>71</v>
+      </c>
+      <c r="F117">
+        <v>100</v>
+      </c>
+      <c r="G117" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>48</v>
+      </c>
+      <c r="B118" t="s">
+        <v>14</v>
+      </c>
+      <c r="C118" t="s">
+        <v>73</v>
+      </c>
+      <c r="E118" t="s">
+        <v>71</v>
+      </c>
+      <c r="F118">
+        <v>100</v>
+      </c>
+      <c r="G118" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>49</v>
+      </c>
+      <c r="B119" t="s">
+        <v>14</v>
+      </c>
+      <c r="C119" t="s">
+        <v>74</v>
+      </c>
+      <c r="E119" t="s">
+        <v>71</v>
+      </c>
+      <c r="F119">
+        <v>100</v>
+      </c>
+      <c r="G119" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>50</v>
+      </c>
+      <c r="B120" t="s">
+        <v>14</v>
+      </c>
+      <c r="C120" t="s">
+        <v>75</v>
+      </c>
+      <c r="E120" t="s">
+        <v>71</v>
+      </c>
+      <c r="F120">
+        <v>100</v>
+      </c>
+      <c r="G120" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>51</v>
+      </c>
+      <c r="B121" t="s">
+        <v>14</v>
+      </c>
+      <c r="C121" t="s">
+        <v>76</v>
+      </c>
+      <c r="E121" t="s">
+        <v>71</v>
+      </c>
+      <c r="F121">
+        <v>100</v>
+      </c>
+      <c r="G121" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>52</v>
+      </c>
+      <c r="B122" t="s">
+        <v>14</v>
+      </c>
+      <c r="C122" t="s">
+        <v>77</v>
+      </c>
+      <c r="E122" t="s">
+        <v>71</v>
+      </c>
+      <c r="F122">
+        <v>100</v>
+      </c>
+      <c r="G122" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>53</v>
+      </c>
+      <c r="B123" t="s">
+        <v>14</v>
+      </c>
+      <c r="C123" t="s">
+        <v>78</v>
+      </c>
+      <c r="E123" t="s">
+        <v>71</v>
+      </c>
+      <c r="F123">
+        <v>100</v>
+      </c>
+      <c r="G123" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>54</v>
+      </c>
+      <c r="B124" t="s">
+        <v>14</v>
+      </c>
+      <c r="C124" t="s">
+        <v>79</v>
+      </c>
+      <c r="E124" t="s">
+        <v>71</v>
+      </c>
+      <c r="F124">
+        <v>100</v>
+      </c>
+      <c r="G124" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>55</v>
+      </c>
+      <c r="B125" t="s">
+        <v>14</v>
+      </c>
+      <c r="C125" t="s">
+        <v>56</v>
+      </c>
+      <c r="E125" t="s">
+        <v>71</v>
+      </c>
+      <c r="F125">
+        <v>100</v>
+      </c>
+      <c r="G125" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>61</v>
+      </c>
+      <c r="B126" t="s">
+        <v>14</v>
+      </c>
+      <c r="C126" t="s">
+        <v>62</v>
+      </c>
+      <c r="E126" t="s">
+        <v>71</v>
+      </c>
+      <c r="F126">
+        <v>100</v>
+      </c>
+      <c r="G126" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>63</v>
+      </c>
+      <c r="B127" t="s">
+        <v>14</v>
+      </c>
+      <c r="C127" t="s">
+        <v>64</v>
+      </c>
+      <c r="E127" t="s">
+        <v>71</v>
+      </c>
+      <c r="F127">
+        <v>100</v>
+      </c>
+      <c r="G127" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>65</v>
+      </c>
+      <c r="B128" t="s">
+        <v>14</v>
+      </c>
+      <c r="C128" t="s">
+        <v>66</v>
+      </c>
+      <c r="E128" t="s">
+        <v>71</v>
+      </c>
+      <c r="F128">
+        <v>100</v>
+      </c>
+      <c r="G128" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>67</v>
+      </c>
+      <c r="B129" t="s">
+        <v>14</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="E129" t="s">
+        <v>71</v>
+      </c>
+      <c r="F129">
+        <v>100</v>
+      </c>
+      <c r="G129" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/resources/analysis_schema_quant_data_analysis_nutrition_template.xlsx
+++ b/resources/analysis_schema_quant_data_analysis_nutrition_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CE1D95-ED12-4115-A1B7-1DCA43E148BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8421CC-AF59-4580-81F6-30A5DE041D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicators" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="81">
   <si>
     <t>indicator_name</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>ecfies_s08</t>
+  </si>
+  <si>
+    <t>select_multiple_cat</t>
   </si>
 </sst>
 </file>
@@ -609,7 +612,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.85546875" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="16.28515625" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
@@ -1132,7 +1135,7 @@
         <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
         <v>64</v>
@@ -1149,7 +1152,7 @@
         <v>65</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
         <v>66</v>
@@ -1166,7 +1169,7 @@
         <v>67</v>
       </c>
       <c r="B33" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s">
         <v>68</v>
@@ -1757,7 +1760,7 @@
         <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="C63" t="s">
         <v>64</v>
@@ -1777,7 +1780,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="C64" t="s">
         <v>66</v>
@@ -1797,7 +1800,7 @@
         <v>67</v>
       </c>
       <c r="B65" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="C65" t="s">
         <v>68</v>
@@ -2391,7 +2394,7 @@
         <v>63</v>
       </c>
       <c r="B95" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="C95" t="s">
         <v>64</v>
@@ -2411,7 +2414,7 @@
         <v>65</v>
       </c>
       <c r="B96" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="C96" t="s">
         <v>66</v>
@@ -3025,7 +3028,7 @@
         <v>63</v>
       </c>
       <c r="B127" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="C127" t="s">
         <v>64</v>
@@ -3045,7 +3048,7 @@
         <v>65</v>
       </c>
       <c r="B128" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="C128" t="s">
         <v>66</v>
@@ -3065,7 +3068,7 @@
         <v>67</v>
       </c>
       <c r="B129" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="C129" t="s">
         <v>68</v>
